--- a/daily_matches/job_matches_2026-10-17.xlsx
+++ b/daily_matches/job_matches_2026-10-17.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,47 +456,47 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Development Engineer- Product Reliability Engineering</t>
+          <t>Application Engineer - AI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Allspring Global Investments Holdings, LLC</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Highlands Ranch, CO, USA USA</t>
+          <t>Charlotte, NC, USA USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>15.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>LangChain, Prompt Engineering, PyTorch, scikit-learn, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>LangChain, RAG, S3, Docker, CI/CD, Jenkins, Terraform, Git, PostgreSQL, Python</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19bb11d6bd744f5f</t>
+          <t>https://www.indeed.com/viewjob?jk=499279ea0bb831c0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Conversational AI Engineer (LLM &amp; GenAI)</t>
+          <t>Senior Software Engineer - Agentic AI and Frontend Applications</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -505,38 +505,38 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Prompt Engineering, TensorFlow, PyTorch, MLflow</t>
+          <t>LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, CI/CD, Git, Snowflake, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58590d983e09d0d2</t>
+          <t>https://www.indeed.com/viewjob?jk=0f9041fd45ab767d</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Digital</t>
+          <t>Mgr - Software Eng</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Floor &amp; Decor</t>
+          <t>Ally Financial</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Atlanta, GA, USA USA</t>
+          <t>Detroit, MI, USA USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -544,29 +544,29 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Copilot, MLflow, CI/CD, Git, Databricks, PySpark, Python</t>
+          <t>Data Scientist, Machine Learning Engineer, LangChain, RAG, LLaMA, Prompt Engineering, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5abc5aa030484718</t>
+          <t>https://www.indeed.com/viewjob?jk=32e7326c6ece402d</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Generative AI Engineer - Graphics</t>
+          <t>AI / Machine Learning Talent</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Ensemble Health Partners</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -575,11 +575,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, TensorFlow, PyTorch, CI/CD, Git, Python, R, C++</t>
+          <t>Data Scientist, Machine Learning Engineer, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -589,32 +589,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=025fafb2ecdf259c</t>
+          <t>https://www.indeed.com/viewjob?jk=1493bb2b3c51f848</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Engineer II</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Vivmark Residential</t>
+          <t>Ross Dress For Less</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA USA</t>
+          <t>Dublin, CA, USA USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, CI/CD, Snowflake, BigQuery, Python, SQL, R, Scala</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, Prompt Engineering, OpenCV, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -624,172 +624,172 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=758796bed3b06a29</t>
+          <t>https://www.indeed.com/viewjob?jk=09cb0db2afcac907</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Gen AI Developer Specialist</t>
+          <t>Senior Data Scientist – Generative AI &amp; LLM Engineering</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Hexaware Technologies</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>Chicago, IL, USA USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, S3, Git, Kafka, NoSQL, Python, SQL, R</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, scikit-learn, Python, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3169bfdad7427759</t>
+          <t>https://www.indeed.com/viewjob?jk=17cecd02e1887d0a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer 1</t>
+          <t>Engineer Sr, Applied Research Science</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Intuit</t>
+          <t>Shure</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Mountain View, CA, USA USA</t>
+          <t>Niles, IL, USA USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, Jenkins, Git, PostgreSQL, MySQL, MongoDB, Python, SQL, R, Java</t>
+          <t>RAG, Copilot, TensorFlow, PyTorch, scikit-learn, Docker, Git, Matplotlib, Python, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4f8ead9fe081bdc</t>
+          <t>https://www.indeed.com/viewjob?jk=ebbae7f2346252b4</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineering III - AWS, GCP, Terraform</t>
+          <t>Senior Cloud Services Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, USA USA</t>
+          <t>KY, USA USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Terraform, Git, PostgreSQL, NoSQL, Python, SQL, R</t>
+          <t>Generative AI, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Databricks, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8af66e2b857b882</t>
+          <t>https://www.indeed.com/viewjob?jk=ff6c8ab87fd251d4</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer II - Python, Databricks, ETL</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA USA</t>
+          <t>Hartford, CT, USA USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Glue, CI/CD, Terraform, Databricks, PySpark, NoSQL, Python, SQL, R</t>
+          <t>RAG, Prompt Engineering, CI/CD, Jenkins, GitHub Actions, Git, MySQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bec91c851aad821</t>
+          <t>https://www.indeed.com/viewjob?jk=6d6df8d550538c2e</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Scientist - Measurement</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>InMarket</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, USA USA</t>
+          <t>Atlanta, GA, USA USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, BigQuery, Git, BigQuery, Python, SQL, R, Bayesian</t>
+          <t>AI Engineer, Generative AI, RAG, Gemini, Snowflake, Databricks, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -799,32 +799,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfe3b0d4c13e431e</t>
+          <t>https://www.indeed.com/viewjob?jk=1abf5c225b429044</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Scientist, Digital</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Floor &amp; Decor</t>
+          <t>Atlas Air, Inc.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Atlanta, GA, USA USA</t>
+          <t>Cincinnati, OH, USA USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, CI/CD, Git, Databricks, PySpark, Python, SQL, R</t>
+          <t>Kinesis, CI/CD, Git, Databricks, Kafka, Python, SQL, R, Java, C++</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -834,102 +834,102 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76f173c083d795f2</t>
+          <t>https://www.indeed.com/viewjob?jk=71b643cc943fe0db</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Business Applications &amp; AI Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Integrated Dermatology</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, USA USA</t>
+          <t>New Orleans, LA, USA USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Copilot, Databricks, Power BI, R, Scala, Optimization</t>
+          <t>AI Engineer, Generative AI, RAG, Gemini, Snowflake, Databricks, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94b249f3181b0ae3</t>
+          <t>https://www.indeed.com/viewjob?jk=f2d8ff32333b0bbf</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Network Site Reliability Engineer, AI Solutions Lab</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Marvell Technology</t>
+          <t>Ally Financial</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, USA USA</t>
+          <t>Detroit, MI, USA USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Copilot, PyTorch, Kubernetes, Terraform, Python, R, C++, Optimization</t>
+          <t>Generative AI, RAG, Copilot, S3, CI/CD, Terraform, Git, PostgreSQL, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba0359210efb08ba</t>
+          <t>https://www.indeed.com/viewjob?jk=701f73a757e3a978</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI Solutions Engineer</t>
+          <t>Software Engineer 1</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Mirion</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>San Diego, CA, USA USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>LangChain, RAG, TensorFlow, PyTorch, OpenCV, Git, Databricks, Python, R</t>
+          <t>Generative AI, Jenkins, Git, PostgreSQL, MySQL, MongoDB, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -939,67 +939,67 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=316b87233c946e3d</t>
+          <t>https://www.indeed.com/viewjob?jk=a75f554c97282bc2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Cyber Security Cloud Engineer</t>
+          <t>Senior AI Engineer, Agentic Healthcare Platform - Remote</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>National Carwash Solutions, Inc.</t>
+          <t>Baylor Scott &amp; White Health</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Atlanta, GA, USA USA</t>
+          <t>Dallas, TX, USA USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
+          <t>AI Engineer, LangChain, RAG, Gemini, Prompt Engineering, FastAPI, Docker, CI/CD, Python, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee1187c9ade4946d</t>
+          <t>https://www.indeed.com/viewjob?jk=0e830aef437fae1d</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Vulnerability Management</t>
+          <t>AI Engineer III</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GitHub</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>New Orleans, LA, USA USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, GitHub Actions, Git, Python, R, Java, C++</t>
+          <t>AI Engineer, RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Terraform, R, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1009,42 +1009,462 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16c2992c50fa7ee8</t>
+          <t>https://www.indeed.com/viewjob?jk=a1fd87eba80653d8</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Product Support Solutions Developer</t>
+          <t>AI Engineer II</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Recorded Future</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Boston, MA, USA USA</t>
+          <t>Las Vegas, NV, USA USA</t>
         </is>
       </c>
       <c r="D18" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Terraform, R, Scala</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9433a2a95dfe0b9b</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>AI Engineer II</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Detroit, MI, USA USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Terraform, R, Scala</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c769b23903df4a93</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Sr Credit Data Scientist</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>WEX Inc.</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Remote, USA USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Gemini, scikit-learn, LightGBM, AWS SageMaker, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=217a810281e242a4</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>AI Engineer III</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, USA USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Terraform, R, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=08f3cf35f8eeb8b0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Lenovo</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Morrisville, NC, USA USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, TensorFlow, PyTorch, Git, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=29b8ad979af342c6</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>AI Engineer II</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>New Orleans, LA, USA USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Terraform, R, Scala</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=18c8f5cd15d15d9f</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Associate Software Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Morningstar</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Chicago, IL, USA USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, Copilot, Git, PostgreSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=384f685ebddb8fe6</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>AI Engineer III</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Las Vegas, NV, USA USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Terraform, R, Scala</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=85cf11ec1c2cfc0f</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Cloud Developer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Vanderbilt University</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Nashville, TN, USA USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
         <v>10</v>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, Prompt Engineering, Tableau, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=db17d3780e550a03</t>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, EC2, CI/CD, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a6141663241f54e2</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Sr Scientist, Tech - Science</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>New York, NY, USA USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Data Scientist, TensorFlow, PyTorch, scikit-learn, Git, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a12e12e2b06e7038</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Associate - Full-Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>New York Life</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>New York, NY, USA USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, RAG, Terraform, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3dca5a9875177819</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer- Rust / C++</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Thomson Reuters</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Eagan, MN, USA USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Git, NoSQL, SQL, R, C++</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2d92a0858909681b</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>AI &amp; Automations Builder (HR)</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>SPS Commerce</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, USA USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, Snowflake, Databricks, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d238613517a2fa41</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-10-17.xlsx
+++ b/daily_matches/job_matches_2026-10-17.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,25 +456,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Application Engineer - AI</t>
+          <t>Data Engineer 4, Real-time Data Platform</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Allspring Global Investments Holdings, LLC</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Charlotte, NC, USA USA</t>
+          <t>Plano, TX, USA USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.6</v>
+        <v>17.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>LangChain, RAG, S3, Docker, CI/CD, Jenkins, Terraform, Git, PostgreSQL, Python</t>
+          <t>Glue, Redshift, CI/CD, Git, Snowflake, Databricks, Redshift, Kafka, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -484,32 +484,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=499279ea0bb831c0</t>
+          <t>https://www.indeed.com/viewjob?jk=84b8331b9f96dda9</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Agentic AI and Frontend Applications</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Atlanta, GA, USA USA</t>
+          <t>Glendale, CA, USA USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, CI/CD, Git, Snowflake, Python</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -519,32 +519,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f9041fd45ab767d</t>
+          <t>https://www.indeed.com/viewjob?jk=9f54ab238ee9d4aa</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Mgr - Software Eng</t>
+          <t>Sr Engineer, ML, SMAI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ally Financial</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Detroit, MI, USA USA</t>
+          <t>Boise, ID, USA USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, LangChain, RAG, LLaMA, Prompt Engineering, Docker, Kubernetes, CI/CD, Git</t>
+          <t>Generative AI, RAG, Prompt Engineering, Dataflow, Docker, Kubernetes, CI/CD, Snowflake, Kafka, SQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -554,32 +554,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32e7326c6ece402d</t>
+          <t>https://www.indeed.com/viewjob?jk=d9675119b3c7180b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI / Machine Learning Talent</t>
+          <t>Data analyst/Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ensemble Health Partners</t>
+          <t>SEGULA Technologies</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Jose, CA, USA USA</t>
+          <t>Auburn Hills, MI, USA USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Python, SQL, R, Java</t>
+          <t>RAG, Dataflow, Git, Snowflake, Databricks, PySpark, Hadoop, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -589,32 +589,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1493bb2b3c51f848</t>
+          <t>https://www.indeed.com/viewjob?jk=126acea1cfb07345</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Engineer II</t>
+          <t>Sr. Software Engineer, MarTech (Remote)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ross Dress For Less</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dublin, CA, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, Prompt Engineering, OpenCV, CI/CD, Git, Python</t>
+          <t>RAG, Prompt Engineering, CI/CD, Jenkins, Git, Snowflake, Databricks, Kafka, Python, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -624,32 +624,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09cb0db2afcac907</t>
+          <t>https://www.indeed.com/viewjob?jk=6f49f444e24197e4</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Scientist – Generative AI &amp; LLM Engineering</t>
+          <t>Software Engineer II - Growth</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>BILL</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, scikit-learn, Python, R</t>
+          <t>Generative AI, RAG, S3, Kinesis, CI/CD, MySQL, NoSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -659,32 +659,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17cecd02e1887d0a</t>
+          <t>https://www.indeed.com/viewjob?jk=2dfbf17c97322483</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Engineer Sr, Applied Research Science</t>
+          <t>AI Engineer III</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Shure</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Niles, IL, USA USA</t>
+          <t>Detroit, MI, USA USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Copilot, TensorFlow, PyTorch, scikit-learn, Docker, Git, Matplotlib, Python, R</t>
+          <t>AI Engineer, RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Terraform, R, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -694,32 +694,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebbae7f2346252b4</t>
+          <t>https://www.indeed.com/viewjob?jk=93631fa5e9e6f5fb</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Cloud Services Engineer</t>
+          <t>API Integration &amp; Agentic AI Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>AAA Washington</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>KY, USA USA</t>
+          <t>Bellevue, WA, USA USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Databricks, Python, SQL</t>
+          <t>AI Engineer, LangChain, RAG, Copilot, CI/CD, GitHub Actions, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -729,32 +729,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff6c8ab87fd251d4</t>
+          <t>https://www.indeed.com/viewjob?jk=0e34fab680b1ca01</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>AI Engineer II</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Hartford, CT, USA USA</t>
+          <t>Jacksonville, FL, USA USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, CI/CD, Jenkins, GitHub Actions, Git, MySQL, Python, SQL, R</t>
+          <t>AI Engineer, RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Terraform, R, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -764,32 +764,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d6df8d550538c2e</t>
+          <t>https://www.indeed.com/viewjob?jk=feed41e065eee097</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Engineer- Software, AI and Data Analytics</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>American Honda Motor</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Atlanta, GA, USA USA</t>
+          <t>East Liberty, OH, USA USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Gemini, Snowflake, Databricks, Tableau, Python, SQL, R</t>
+          <t>CI/CD, Databricks, Kafka, Tableau, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -799,672 +799,42 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1abf5c225b429044</t>
+          <t>https://www.indeed.com/viewjob?jk=73b6de841a3a14d0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Platform Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Atlas Air, Inc.</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, USA USA</t>
+          <t>Nashville, TN, USA USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kinesis, CI/CD, Git, Databricks, Kafka, Python, SQL, R, Java, C++</t>
+          <t>Generative AI, RAG, Kubernetes, Terraform, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71b643cc943fe0db</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Data Engineer II</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>New Orleans, LA, USA USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, RAG, Gemini, Snowflake, Databricks, Tableau, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f2d8ff32333b0bbf</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Ally Financial</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Detroit, MI, USA USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Copilot, S3, CI/CD, Terraform, Git, PostgreSQL, SQL, R</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=701f73a757e3a978</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Software Engineer 1</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Intuit</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>San Diego, CA, USA USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Generative AI, Jenkins, Git, PostgreSQL, MySQL, MongoDB, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a75f554c97282bc2</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Senior AI Engineer, Agentic Healthcare Platform - Remote</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Baylor Scott &amp; White Health</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Dallas, TX, USA USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>AI Engineer, LangChain, RAG, Gemini, Prompt Engineering, FastAPI, Docker, CI/CD, Python, R</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0e830aef437fae1d</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>AI Engineer III</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>New Orleans, LA, USA USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Terraform, R, Scala</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a1fd87eba80653d8</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>AI Engineer II</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Las Vegas, NV, USA USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Terraform, R, Scala</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9433a2a95dfe0b9b</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>AI Engineer II</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Detroit, MI, USA USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Terraform, R, Scala</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c769b23903df4a93</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Sr Credit Data Scientist</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>WEX Inc.</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Remote, USA USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Gemini, scikit-learn, LightGBM, AWS SageMaker, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=217a810281e242a4</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>AI Engineer III</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Jacksonville, FL, USA USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Terraform, R, Scala</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=08f3cf35f8eeb8b0</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>AI Engineer</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Lenovo</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Morrisville, NC, USA USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, TensorFlow, PyTorch, Git, Python, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=29b8ad979af342c6</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>AI Engineer II</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>New Orleans, LA, USA USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Terraform, R, Scala</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=18c8f5cd15d15d9f</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Associate Software Engineer</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Morningstar</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Chicago, IL, USA USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Generative AI, LangChain, RAG, Copilot, Git, PostgreSQL, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=384f685ebddb8fe6</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>AI Engineer III</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Las Vegas, NV, USA USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Terraform, R, Scala</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=85cf11ec1c2cfc0f</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Cloud Developer</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Vanderbilt University</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Nashville, TN, USA USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>10</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, S3, EC2, CI/CD, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a6141663241f54e2</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Sr Scientist, Tech - Science</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Uber</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>New York, NY, USA USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>10</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Data Scientist, TensorFlow, PyTorch, scikit-learn, Git, PySpark, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a12e12e2b06e7038</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Associate - Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>New York Life</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>New York, NY, USA USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>10</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Data Scientist, LangChain, RAG, Terraform, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3dca5a9875177819</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer- Rust / C++</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Thomson Reuters</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Eagan, MN, USA USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>10</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Kubernetes, CI/CD, Git, NoSQL, SQL, R, C++</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2d92a0858909681b</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>AI &amp; Automations Builder (HR)</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>SPS Commerce</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Minneapolis, MN, USA USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>10</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>AI Engineer, LangChain, Snowflake, Databricks, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d238613517a2fa41</t>
+          <t>https://www.indeed.com/viewjob?jk=38a524915d809335</t>
         </is>
       </c>
     </row>
